--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104699_W27.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104699_W27.xlsx
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9944</v>
+        <v>3.0061</v>
       </c>
       <c r="E2" t="n">
-        <v>3.6351</v>
+        <v>3.4796</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.6407</v>
+        <v>-0.4735</v>
       </c>
       <c r="G2" t="n">
-        <v>1.7257</v>
+        <v>1.7216</v>
       </c>
       <c r="H2" t="n">
-        <v>2.2268</v>
+        <v>2.2096</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.501</v>
+        <v>-0.488</v>
       </c>
       <c r="J2" t="n">
-        <v>3.1291</v>
+        <v>3.0945</v>
       </c>
       <c r="K2" t="n">
-        <v>2.9052</v>
+        <v>2.8711</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2239</v>
+        <v>0.2234</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.4034</v>
+        <v>-1.3729</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.6785</v>
+        <v>-0.6615</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.7249</v>
+        <v>-0.7114</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.0415</v>
+        <v>-2.0487</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S2" t="n">
-        <v>1.6562</v>
+        <v>1.6699</v>
       </c>
       <c r="T2" t="n">
-        <v>1.4548</v>
+        <v>1.3443</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2014</v>
+        <v>0.3256</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W2" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R. NETO</t>
+          <t>J. AXEL GUDMUNDSSON</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2747</v>
+        <v>2.4508</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1457</v>
+        <v>2.4146</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.871</v>
+        <v>0.0362</v>
       </c>
       <c r="G3" t="n">
-        <v>3.3732</v>
+        <v>-0.6686</v>
       </c>
       <c r="H3" t="n">
-        <v>1.6939</v>
+        <v>-0.7906</v>
       </c>
       <c r="I3" t="n">
-        <v>1.6793</v>
+        <v>0.122</v>
       </c>
       <c r="J3" t="n">
-        <v>3.9984</v>
+        <v>1.7229</v>
       </c>
       <c r="K3" t="n">
-        <v>2.0261</v>
+        <v>-0.2725</v>
       </c>
       <c r="L3" t="n">
-        <v>1.9724</v>
+        <v>1.9955</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.6252</v>
+        <v>-2.3915</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3321</v>
+        <v>-0.518</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2931</v>
+        <v>-1.8734</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.2268</v>
+        <v>0.9105</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.361</v>
+        <v>-0.9105</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1342</v>
+        <v>1.8211</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5541</v>
+        <v>1.1194</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9739</v>
+        <v>0.5128</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4198</v>
+        <v>0.6066</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.3176</v>
+        <v>1.0895</v>
       </c>
       <c r="W3" t="n">
-        <v>0.4822</v>
+        <v>1.0895</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.7997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. RUBIO</t>
+          <t>R. NETO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2052</v>
+        <v>1.8015</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2611</v>
+        <v>2.887</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0559</v>
+        <v>-1.0855</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.8992</v>
+        <v>3.3756</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.4647</v>
+        <v>1.6999</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4345</v>
+        <v>1.6757</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.6625</v>
+        <v>3.9749</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0866</v>
+        <v>2.0167</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.749</v>
+        <v>1.9582</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2368</v>
+        <v>-0.5993000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5513</v>
+        <v>-0.3168</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3145</v>
+        <v>-0.2826</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2268</v>
+        <v>-1.3658</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2268</v>
+        <v>1.1382</v>
       </c>
       <c r="S4" t="n">
-        <v>2.1044</v>
+        <v>-0.0278</v>
       </c>
       <c r="T4" t="n">
-        <v>2.1504</v>
+        <v>-0.1955</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.046</v>
+        <v>0.1677</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-1.3187</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.4733</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="5">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9695</v>
+        <v>1.3973</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3019</v>
+        <v>0.5294</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6676</v>
+        <v>0.8678</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2102</v>
+        <v>1.2138</v>
       </c>
       <c r="H5" t="n">
-        <v>1.0316</v>
+        <v>1.0366</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1786</v>
+        <v>0.1772</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7192</v>
+        <v>0.7108</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7966</v>
+        <v>0.7929</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.07729999999999999</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>0.491</v>
+        <v>0.503</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2351</v>
+        <v>0.2437</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2559</v>
+        <v>0.2593</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4676</v>
+        <v>-0.0441</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4174</v>
+        <v>-0.1813</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0502</v>
+        <v>0.1372</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. AXEL GUDMUNDSSON</t>
+          <t>J. SAMUELS JR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8955</v>
+        <v>1.1051</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8333</v>
+        <v>0.9801</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0621</v>
+        <v>0.125</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.6787</v>
+        <v>-1.1662</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.8038999999999999</v>
+        <v>1.344</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1253</v>
+        <v>-2.5102</v>
       </c>
       <c r="J6" t="n">
-        <v>1.7428</v>
+        <v>1.2269</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.2669</v>
+        <v>2.2925</v>
       </c>
       <c r="L6" t="n">
-        <v>2.0097</v>
+        <v>-1.0656</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.4215</v>
+        <v>-2.3931</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5371</v>
+        <v>-0.9485</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.8844</v>
+        <v>-1.4446</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9073</v>
+        <v>0.4553</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9073</v>
+        <v>-1.8211</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8147</v>
+        <v>2.2763</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4258</v>
+        <v>0.5688</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.0948</v>
+        <v>0.3271</v>
       </c>
       <c r="U6" t="n">
-        <v>0.669</v>
+        <v>0.2418</v>
       </c>
       <c r="V6" t="n">
-        <v>1.0927</v>
+        <v>1.2472</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0927</v>
+        <v>1.2472</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. SAMUELS JR</t>
+          <t>J. RUBIO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5603</v>
+        <v>0.3322</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5891</v>
+        <v>0.3184</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0288</v>
+        <v>0.0138</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.1637</v>
+        <v>-0.8964</v>
       </c>
       <c r="H7" t="n">
-        <v>1.3419</v>
+        <v>-0.4598</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.5056</v>
+        <v>-0.4365</v>
       </c>
       <c r="J7" t="n">
-        <v>1.2501</v>
+        <v>-0.6662</v>
       </c>
       <c r="K7" t="n">
-        <v>2.3031</v>
+        <v>0.0862</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.053</v>
+        <v>-0.7524</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.4139</v>
+        <v>-0.2301</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9612000000000001</v>
+        <v>-0.546</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.4526</v>
+        <v>0.3159</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4537</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.8147</v>
+        <v>-0.2276</v>
       </c>
       <c r="R7" t="n">
-        <v>2.2683</v>
+        <v>0.2276</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0169</v>
+        <v>1.2286</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0998</v>
+        <v>1.2122</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1167</v>
+        <v>0.0163</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2534</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2534</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.8368</v>
+        <v>-2.1199</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0895</v>
+        <v>-0.4565</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.7473</v>
+        <v>-1.6635</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.6577</v>
+        <v>-2.692</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.9507</v>
+        <v>-2.9606</v>
       </c>
       <c r="I8" t="n">
-        <v>0.293</v>
+        <v>0.2685</v>
       </c>
       <c r="J8" t="n">
-        <v>1.136</v>
+        <v>1.0611</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.5319</v>
+        <v>-1.5663</v>
       </c>
       <c r="L8" t="n">
-        <v>2.6679</v>
+        <v>2.6274</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.7937</v>
+        <v>-3.7531</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.4188</v>
+        <v>-1.3943</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.3749</v>
+        <v>-2.3588</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="R8" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S8" t="n">
-        <v>1.8416</v>
+        <v>1.5965</v>
       </c>
       <c r="T8" t="n">
-        <v>1.4245</v>
+        <v>1.1489</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4171</v>
+        <v>0.4476</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.9281</v>
+        <v>-1.9349</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.8354</v>
+        <v>-0.8454</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="9">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.342</v>
+        <v>-2.3023</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.8859</v>
+        <v>-1.8236</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4561</v>
+        <v>-0.4786</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.9835</v>
+        <v>-0.984</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.0822</v>
+        <v>-1.0855</v>
       </c>
       <c r="I9" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.1014</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.5381</v>
+        <v>-1.5448</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.5381</v>
+        <v>-1.5448</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.5546</v>
+        <v>0.5608</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4559</v>
+        <v>0.4593</v>
       </c>
       <c r="O9" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.1014</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4927</v>
+        <v>-0.4564</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3478</v>
+        <v>-0.2788</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1449</v>
+        <v>-0.1775</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L. FISCHER</t>
+          <t>D. DIEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3558</v>
+        <v>-3.0056</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3881</v>
+        <v>-1.4996</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.9677</v>
+        <v>-1.5061</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.2647</v>
+        <v>-4.1183</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.8627</v>
+        <v>-1.3641</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.402</v>
+        <v>-2.7542</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.3972</v>
+        <v>-2.3714</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.5464</v>
+        <v>-0.9038</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1493</v>
+        <v>-1.4676</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.8675</v>
+        <v>-1.7469</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3162</v>
+        <v>-0.4603</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.5513</v>
+        <v>-1.2866</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>0.2276</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1342</v>
+        <v>-0.2276</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1342</v>
+        <v>0.4553</v>
       </c>
       <c r="S10" t="n">
-        <v>2.4553</v>
+        <v>0.498</v>
       </c>
       <c r="T10" t="n">
-        <v>2.0506</v>
+        <v>0.5547</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4047</v>
+        <v>-0.0567</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5463</v>
+        <v>0.387</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0927</v>
+        <v>0.5447</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.639</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. DIEZ</t>
+          <t>L. FISCHER</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.0546</v>
+        <v>-4.3537</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.4296</v>
+        <v>-2.1629</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.625</v>
+        <v>-2.1908</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.1168</v>
+        <v>-4.2686</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.3607</v>
+        <v>-2.8716</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.7561</v>
+        <v>-1.397</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.3479</v>
+        <v>-2.4203</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.8871</v>
+        <v>-2.5693</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.4608</v>
+        <v>0.1489</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.7689</v>
+        <v>-1.8483</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4735</v>
+        <v>-0.3023</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.2954</v>
+        <v>-1.546</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2268</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.2268</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4537</v>
+        <v>1.1382</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4497</v>
+        <v>0.4596</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5989</v>
+        <v>0.3061</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1491</v>
+        <v>0.1535</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3856</v>
+        <v>-0.5447</v>
       </c>
       <c r="W11" t="n">
-        <v>0.5463</v>
+        <v>1.0895</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.1607</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.1986</v>
+        <v>-5.511</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.1767</v>
+        <v>-4.5034</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0218</v>
+        <v>-1.0076</v>
       </c>
       <c r="G12" t="n">
-        <v>-5.4197</v>
+        <v>-5.4337</v>
       </c>
       <c r="H12" t="n">
-        <v>1.7374</v>
+        <v>1.7349</v>
       </c>
       <c r="I12" t="n">
-        <v>-7.157</v>
+        <v>-7.1685</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.5505</v>
+        <v>-2.5989</v>
       </c>
       <c r="K12" t="n">
-        <v>2.1331</v>
+        <v>2.1094</v>
       </c>
       <c r="L12" t="n">
-        <v>-4.6835</v>
+        <v>-4.7083</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.8692</v>
+        <v>-2.8348</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.3957</v>
+        <v>-0.3745</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.4735</v>
+        <v>-2.4603</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="R12" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3687</v>
+        <v>0.3308</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5867</v>
+        <v>0.1457</v>
       </c>
       <c r="U12" t="n">
-        <v>0.218</v>
+        <v>0.1851</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.3176</v>
+        <v>-1.3187</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.2249</v>
+        <v>-0.2292</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.8882</v>
+        <v>-7.1995</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.2035999999999998</v>
+        <v>0.1630999999999991</v>
       </c>
       <c r="F13" t="n">
-        <v>-7.6846</v>
+        <v>-7.3628</v>
       </c>
       <c r="G13" t="n">
-        <v>-13.8749</v>
+        <v>-13.9168</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.493299999999999</v>
+        <v>-1.5072</v>
       </c>
       <c r="I13" t="n">
-        <v>-12.3814</v>
+        <v>-12.4096</v>
       </c>
       <c r="J13" t="n">
-        <v>2.4794</v>
+        <v>2.1895</v>
       </c>
       <c r="K13" t="n">
-        <v>3.480300000000001</v>
+        <v>3.3121</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.0004</v>
+        <v>-1.122600000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>-16.3545</v>
+        <v>-16.1062</v>
       </c>
       <c r="N13" t="n">
-        <v>-4.973399999999999</v>
+        <v>-4.8192</v>
       </c>
       <c r="O13" t="n">
-        <v>-11.3811</v>
+        <v>-11.2871</v>
       </c>
       <c r="P13" t="n">
-        <v>3.4024</v>
+        <v>3.4144</v>
       </c>
       <c r="Q13" t="n">
-        <v>-11.3417</v>
+        <v>-11.3817</v>
       </c>
       <c r="R13" t="n">
-        <v>14.7442</v>
+        <v>14.7962</v>
       </c>
       <c r="S13" t="n">
-        <v>6.215199999999999</v>
+        <v>6.9433</v>
       </c>
       <c r="T13" t="n">
-        <v>4.158799999999999</v>
+        <v>4.896199999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>2.0565</v>
+        <v>2.0472</v>
       </c>
       <c r="V13" t="n">
-        <v>-3.6313</v>
+        <v>-3.6406</v>
       </c>
       <c r="W13" t="n">
-        <v>4.499700000000001</v>
+        <v>4.4591</v>
       </c>
       <c r="X13" t="n">
-        <v>-8.1309</v>
+        <v>-8.099699999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.4535</v>
+        <v>8.0235</v>
       </c>
       <c r="E14" t="n">
-        <v>5.8125</v>
+        <v>6.3418</v>
       </c>
       <c r="F14" t="n">
-        <v>1.641</v>
+        <v>1.6817</v>
       </c>
       <c r="G14" t="n">
-        <v>9.1853</v>
+        <v>9.181900000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>1.1861</v>
+        <v>1.1889</v>
       </c>
       <c r="I14" t="n">
-        <v>7.9992</v>
+        <v>7.993</v>
       </c>
       <c r="J14" t="n">
-        <v>8.6159</v>
+        <v>8.5756</v>
       </c>
       <c r="K14" t="n">
-        <v>1.2672</v>
+        <v>1.2476</v>
       </c>
       <c r="L14" t="n">
-        <v>7.3487</v>
+        <v>7.328</v>
       </c>
       <c r="M14" t="n">
-        <v>0.5693</v>
+        <v>0.6063</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.08119999999999999</v>
+        <v>-0.0587</v>
       </c>
       <c r="O14" t="n">
-        <v>0.6505</v>
+        <v>0.665</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.0415</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.7149</v>
+        <v>-1.1308</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9739</v>
+        <v>-0.3836</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.741</v>
+        <v>-0.7472</v>
       </c>
       <c r="V14" t="n">
-        <v>2.0246</v>
+        <v>2.0212</v>
       </c>
       <c r="W14" t="n">
-        <v>1.7997</v>
+        <v>1.792</v>
       </c>
       <c r="X14" t="n">
-        <v>0.2249</v>
+        <v>0.2292</v>
       </c>
     </row>
     <row r="15">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.2728</v>
+        <v>5.6937</v>
       </c>
       <c r="E15" t="n">
-        <v>3.9439</v>
+        <v>4.3822</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3289</v>
+        <v>1.3114</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8124</v>
+        <v>0.837</v>
       </c>
       <c r="H15" t="n">
-        <v>1.0228</v>
+        <v>1.0361</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2105</v>
+        <v>-0.1991</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6348</v>
+        <v>0.6146</v>
       </c>
       <c r="K15" t="n">
-        <v>0.7895</v>
+        <v>0.7789</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.1547</v>
+        <v>-0.1643</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1776</v>
+        <v>0.2224</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2334</v>
+        <v>0.2572</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.0558</v>
+        <v>-0.0348</v>
       </c>
       <c r="P15" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.2712</v>
+        <v>-0.867</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8347</v>
+        <v>-0.3627</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4365</v>
+        <v>-0.5044</v>
       </c>
       <c r="V15" t="n">
-        <v>4.3707</v>
+        <v>4.3579</v>
       </c>
       <c r="W15" t="n">
-        <v>4.3707</v>
+        <v>4.3579</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1657,58 +1657,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.9813</v>
+        <v>1.9474</v>
       </c>
       <c r="E16" t="n">
-        <v>2.5018</v>
+        <v>2.253</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5205</v>
+        <v>-0.3056</v>
       </c>
       <c r="G16" t="n">
-        <v>1.5763</v>
+        <v>1.5885</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.7129</v>
+        <v>-1.7037</v>
       </c>
       <c r="I16" t="n">
-        <v>3.2893</v>
+        <v>3.2922</v>
       </c>
       <c r="J16" t="n">
-        <v>3.0038</v>
+        <v>2.9919</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.5786</v>
+        <v>-0.5828</v>
       </c>
       <c r="L16" t="n">
-        <v>3.5824</v>
+        <v>3.5747</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.4275</v>
+        <v>-1.4034</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.1344</v>
+        <v>-1.1209</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2931</v>
+        <v>-0.2826</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0487</v>
+        <v>-0.0964</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0484</v>
+        <v>-0.2837</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0003</v>
+        <v>0.1873</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8917</v>
+        <v>0.2186</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.2485</v>
+        <v>-1.763</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1402</v>
+        <v>1.9815</v>
       </c>
       <c r="G17" t="n">
-        <v>2.4309</v>
+        <v>2.4256</v>
       </c>
       <c r="H17" t="n">
-        <v>2.0363</v>
+        <v>2.02</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3946</v>
+        <v>0.4057</v>
       </c>
       <c r="J17" t="n">
-        <v>1.9026</v>
+        <v>1.8749</v>
       </c>
       <c r="K17" t="n">
-        <v>1.1562</v>
+        <v>1.1302</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7463</v>
+        <v>0.7447</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5283</v>
+        <v>0.5507</v>
       </c>
       <c r="N17" t="n">
-        <v>0.88</v>
+        <v>0.8898</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3517</v>
+        <v>-0.3391</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.9488</v>
+        <v>-2.9592</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6384</v>
+        <v>-0.0218</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0907</v>
+        <v>-0.3812</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5477</v>
+        <v>0.3594</v>
       </c>
       <c r="V17" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X17" t="n">
-        <v>0.6105</v>
+        <v>0.6162</v>
       </c>
     </row>
     <row r="18">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7105</v>
+        <v>0.1265</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5646</v>
+        <v>0.8277</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.8541</v>
+        <v>-0.7012</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.179</v>
+        <v>-0.1815</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.8108</v>
+        <v>-0.8209</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6318</v>
+        <v>0.6394</v>
       </c>
       <c r="J18" t="n">
-        <v>1.3631</v>
+        <v>1.3378</v>
       </c>
       <c r="K18" t="n">
-        <v>0.654</v>
+        <v>0.6303</v>
       </c>
       <c r="L18" t="n">
-        <v>0.709</v>
+        <v>0.7075</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.542</v>
+        <v>-1.5193</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.4648</v>
+        <v>-1.4511</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0772</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R18" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5039</v>
+        <v>-0.079</v>
       </c>
       <c r="T18" t="n">
-        <v>1.0162</v>
+        <v>0.311</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5123</v>
+        <v>-0.3899</v>
       </c>
       <c r="V18" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W18" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. ARANITOVIC</t>
+          <t>M. ANDRIC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.038</v>
+        <v>-0.1978</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.6869</v>
+        <v>0.0523</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6489</v>
+        <v>-0.2501</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.7379</v>
+        <v>-0.6512</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.0231</v>
+        <v>-1.2816</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2852</v>
+        <v>0.6304</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.3603</v>
+        <v>-0.168</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.88</v>
+        <v>-0.5623</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5197000000000001</v>
+        <v>0.3943</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.3776</v>
+        <v>-0.4831</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1431</v>
+        <v>-0.7193000000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2345</v>
+        <v>0.2361</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6805</v>
+        <v>1.8211</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6805</v>
+        <v>2.0487</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0194</v>
+        <v>-1.7546</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3266</v>
+        <v>-0.6415</v>
       </c>
       <c r="U19" t="n">
-        <v>0.346</v>
+        <v>-1.1132</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.387</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B. DIBBA</t>
+          <t>A. ARANITOVIC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6102</v>
+        <v>-0.3512</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2357</v>
+        <v>-0.5833</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8459</v>
+        <v>0.2321</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.8774</v>
+        <v>-0.7322</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4429</v>
+        <v>-1.0198</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4345</v>
+        <v>0.2876</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.9711</v>
+        <v>-0.3762</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.222</v>
+        <v>-0.8898</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.749</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>0.09370000000000001</v>
+        <v>-0.356</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2209</v>
+        <v>-0.13</v>
       </c>
       <c r="O20" t="n">
-        <v>0.3145</v>
+        <v>-0.226</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.2268</v>
+        <v>0.6829</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.2268</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>0.6829</v>
       </c>
       <c r="S20" t="n">
-        <v>1.5866</v>
+        <v>-0.302</v>
       </c>
       <c r="T20" t="n">
-        <v>1.4336</v>
+        <v>-0.2072</v>
       </c>
       <c r="U20" t="n">
-        <v>0.153</v>
+        <v>-0.0948</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. APIC</t>
+          <t>D. MAVRA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.881</v>
+        <v>-0.5945</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.4283</v>
+        <v>-1.0914</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4527</v>
+        <v>0.4968</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0527</v>
+        <v>3.7067</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.7937</v>
+        <v>2.3918</v>
       </c>
       <c r="I21" t="n">
-        <v>0.741</v>
+        <v>1.3149</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.5705</v>
+        <v>3.1436</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6825</v>
+        <v>2.8096</v>
       </c>
       <c r="L21" t="n">
-        <v>0.112</v>
+        <v>0.334</v>
       </c>
       <c r="M21" t="n">
-        <v>0.5178</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1113</v>
+        <v>-0.4179</v>
       </c>
       <c r="O21" t="n">
-        <v>0.6291</v>
+        <v>0.9809</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2268</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.2268</v>
+        <v>-3.8697</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4537</v>
+        <v>1.5934</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0375</v>
+        <v>-1.1646</v>
       </c>
       <c r="T21" t="n">
-        <v>0.369</v>
+        <v>-0.523</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3315</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.0927</v>
+        <v>-0.8603</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0927</v>
+        <v>-1.018</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. ANDRIC</t>
+          <t>D. APIC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.2524</v>
+        <v>-1.2308</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.3931</v>
+        <v>-0.6676</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8593</v>
+        <v>-0.5632</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.6693</v>
+        <v>-0.0439</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.2931</v>
+        <v>-0.7873</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6238</v>
+        <v>0.7433999999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.146</v>
+        <v>-0.5745</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.551</v>
+        <v>-0.6862</v>
       </c>
       <c r="L22" t="n">
-        <v>0.4051</v>
+        <v>0.1117</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.5233</v>
+        <v>0.5306</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.742</v>
+        <v>-0.1011</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2187</v>
+        <v>0.6317</v>
       </c>
       <c r="P22" t="n">
-        <v>1.8147</v>
+        <v>0.2276</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R22" t="n">
-        <v>2.0415</v>
+        <v>0.4553</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.7834</v>
+        <v>-0.3251</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.113</v>
+        <v>0.1345</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.6704</v>
+        <v>-0.4596</v>
       </c>
       <c r="V22" t="n">
-        <v>0.3856</v>
+        <v>-1.0895</v>
       </c>
       <c r="W22" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.7071</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D. MAVRA</t>
+          <t>B. DIBBA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.6827</v>
+        <v>-1.433</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.6261</v>
+        <v>-0.7225</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0565</v>
+        <v>-0.7105</v>
       </c>
       <c r="G23" t="n">
-        <v>3.7039</v>
+        <v>-0.887</v>
       </c>
       <c r="H23" t="n">
-        <v>2.3792</v>
+        <v>-0.4505</v>
       </c>
       <c r="I23" t="n">
-        <v>1.3247</v>
+        <v>-0.4365</v>
       </c>
       <c r="J23" t="n">
-        <v>3.1823</v>
+        <v>-0.9872</v>
       </c>
       <c r="K23" t="n">
-        <v>2.8226</v>
+        <v>-0.2348</v>
       </c>
       <c r="L23" t="n">
-        <v>0.3596</v>
+        <v>-0.7524</v>
       </c>
       <c r="M23" t="n">
-        <v>0.5217000000000001</v>
+        <v>0.1002</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.4434</v>
+        <v>-0.2157</v>
       </c>
       <c r="O23" t="n">
-        <v>0.9651</v>
+        <v>0.3159</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.2683</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.8562</v>
+        <v>-0.2276</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5878</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.2505</v>
+        <v>0.7711</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.113</v>
+        <v>0.4923</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.1375</v>
+        <v>0.2788</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.8678</v>
+        <v>-1.0895</v>
       </c>
       <c r="W23" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0285</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.9572</v>
+        <v>-3.5162</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.9908</v>
+        <v>-1.6666</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.9664</v>
+        <v>-1.8496</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.3177</v>
+        <v>-1.3271</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9453</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.263</v>
+        <v>-2.2612</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.3001</v>
+        <v>-0.3262</v>
       </c>
       <c r="K24" t="n">
-        <v>1.198</v>
+        <v>1.1786</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.4981</v>
+        <v>-1.5048</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.0176</v>
+        <v>-1.0009</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.2526</v>
+        <v>-0.2446</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.7649</v>
+        <v>-0.7563</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R24" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9324</v>
+        <v>-0.4866</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5565</v>
+        <v>-0.2023</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3759</v>
+        <v>-0.2843</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>7.888299999999999</v>
+        <v>8.686200000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>7.684799999999999</v>
+        <v>7.3626</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2035999999999996</v>
+        <v>1.3233</v>
       </c>
       <c r="G25" t="n">
-        <v>13.8748</v>
+        <v>13.9168</v>
       </c>
       <c r="H25" t="n">
-        <v>1.4932</v>
+        <v>1.507</v>
       </c>
       <c r="I25" t="n">
-        <v>12.3816</v>
+        <v>12.4098</v>
       </c>
       <c r="J25" t="n">
-        <v>16.3545</v>
+        <v>16.1063</v>
       </c>
       <c r="K25" t="n">
-        <v>4.9734</v>
+        <v>4.8193</v>
       </c>
       <c r="L25" t="n">
-        <v>11.381</v>
+        <v>11.287</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.4796</v>
+        <v>-2.1895</v>
       </c>
       <c r="N25" t="n">
-        <v>-3.4803</v>
+        <v>-3.3123</v>
       </c>
       <c r="O25" t="n">
-        <v>1.0007</v>
+        <v>1.1227</v>
       </c>
       <c r="P25" t="n">
-        <v>-3.402400000000001</v>
+        <v>-3.414400000000001</v>
       </c>
       <c r="Q25" t="n">
-        <v>-14.7441</v>
+        <v>-14.796</v>
       </c>
       <c r="R25" t="n">
-        <v>11.3416</v>
+        <v>11.3816</v>
       </c>
       <c r="S25" t="n">
-        <v>-6.2153</v>
+        <v>-5.4568</v>
       </c>
       <c r="T25" t="n">
-        <v>-2.0566</v>
+        <v>-2.0474</v>
       </c>
       <c r="U25" t="n">
-        <v>-4.1587</v>
+        <v>-3.4095</v>
       </c>
       <c r="V25" t="n">
-        <v>3.631100000000001</v>
+        <v>3.640499999999999</v>
       </c>
       <c r="W25" t="n">
-        <v>8.130800000000001</v>
+        <v>8.099699999999999</v>
       </c>
       <c r="X25" t="n">
-        <v>-4.4997</v>
+        <v>-4.4591</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104699_W27.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104699_W27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104699_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104699_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104699_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104699_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104699_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104699_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104699_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104699_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104699_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104699_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104699_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-8.099699999999999</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0.2292</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104699_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104699_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104699_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0.6162</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104699_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104699_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104699_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104699_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.018</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104699_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104699_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104699_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104699_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-4.4591</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
